--- a/AAII_Financials/Yearly/RBRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RBRK_YR_FIN.xlsx
@@ -928,13 +928,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>25200</v>
+        <v>17700</v>
       </c>
       <c r="E15" s="3">
-        <v>21100</v>
+        <v>17400</v>
       </c>
       <c r="F15" s="3">
-        <v>18400</v>
+        <v>16700</v>
       </c>
       <c r="G15" s="3">
         <v>16300</v>
@@ -1087,13 +1087,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-329500</v>
+        <v>-337000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1111500</v>
+        <v>-1115200</v>
       </c>
       <c r="F21" s="3">
-        <v>-290000</v>
+        <v>-291700</v>
       </c>
       <c r="G21" s="3">
         <v>-246300</v>
